--- a/request_forms/008_envelope_efficiency_registration_form--request_forms.xlsx
+++ b/request_forms/008_envelope_efficiency_registration_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>postal</t>
+          <t>province_state</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Postal</t>
+          <t>Province/State</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>province</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Province</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>province_state</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>first_name_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>First Name 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>province_state_options</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Province</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>address_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>city_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>City 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>postal_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Postal</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,154 +934,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>country_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>postal</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Postal</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>province</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Province</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>province_state</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Zip</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1101,9 +963,9 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'alberta'}</t>
+          <t>alberta</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Alberta'}</t>
+          <t>Alberta</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'british_columbia'}</t>
+          <t>british_columbia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'British Columbia'}</t>
+          <t>British Columbia</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'ontario'}</t>
+          <t>ontario</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Ontario'}</t>
+          <t>Ontario</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'quebec'}</t>
+          <t>quebec</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Quebec'}</t>
+          <t>Quebec</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'save_for_later'}</t>
+          <t>save_for_later</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Save for Later'}</t>
+          <t>Save for Later</t>
         </is>
       </c>
     </row>
@@ -1233,80 +1095,80 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>province_state_choices</t>
+          <t>province_state_options_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'alberta'}</t>
+          <t>alberta</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Alberta'}</t>
+          <t>Alberta</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>province_state_choices</t>
+          <t>province_state_options_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'british_columbia'}</t>
+          <t>british_columbia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'British Columbia'}</t>
+          <t>British Columbia</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>province_state_choices</t>
+          <t>province_state_options_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'ontario'}</t>
+          <t>ontario</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Ontario'}</t>
+          <t>Ontario</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>province_state_choices</t>
+          <t>province_state_options_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'quebec'}</t>
+          <t>quebec</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Quebec'}</t>
+          <t>Quebec</t>
         </is>
       </c>
     </row>
